--- a/كيمياء ترم ثاني.xlsx
+++ b/كيمياء ترم ثاني.xlsx
@@ -2891,22 +2891,22 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I9">
         <v>14</v>
       </c>
       <c r="J9">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K9">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -7839,7 +7839,7 @@
         <v>28</v>
       </c>
       <c r="K24">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -7909,7 +7909,7 @@
         <v>27</v>
       </c>
       <c r="K26">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
@@ -7979,7 +7979,7 @@
         <v>21</v>
       </c>
       <c r="K28">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
@@ -8084,7 +8084,7 @@
         <v>22</v>
       </c>
       <c r="K31">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -8206,7 +8206,7 @@
         <v>27</v>
       </c>
       <c r="K3">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -8241,7 +8241,7 @@
         <v>21</v>
       </c>
       <c r="K4">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -8311,7 +8311,7 @@
         <v>14</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -8346,7 +8346,7 @@
         <v>25</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -8381,7 +8381,7 @@
         <v>13</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -8451,7 +8451,7 @@
         <v>22</v>
       </c>
       <c r="K10">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -8661,7 +8661,7 @@
         <v>25</v>
       </c>
       <c r="K16">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
